--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -51,12 +51,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">area</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rack</t>
+          <t xml:space="preserve">location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -3,13 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="boxes" sheetId="1" r:id="rId1"/>
-    <sheet name="Baro CELLS #1 (-80)" sheetId="2" r:id="rId2"/>
-    <sheet name="UMUT CAA CELLS" sheetId="3" r:id="rId3"/>
-    <sheet name="UMUT CELLS -80" sheetId="4" r:id="rId4"/>
-    <sheet name="DUZENLE" sheetId="5" r:id="rId5"/>
-    <sheet name="ONGOING" sheetId="6" r:id="rId6"/>
-    <sheet name="UMUT CELLS -4-" sheetId="7" r:id="rId7"/>
-    <sheet name="Unnamed box" sheetId="8" r:id="rId8"/>
+    <sheet name="UMUT CAA CELLS" sheetId="2" r:id="rId2"/>
+    <sheet name="UMUT CELLS -80" sheetId="3" r:id="rId3"/>
+    <sheet name="DUZENLE" sheetId="4" r:id="rId4"/>
+    <sheet name="ONGOING" sheetId="5" r:id="rId5"/>
+    <sheet name="UMUT CELLS -4-" sheetId="6" r:id="rId6"/>
+    <sheet name="Unnamed box" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -105,22 +104,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
+          <t xml:space="preserve">UMUT CAA CELLS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">baris</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
       <c r="E2">
@@ -130,29 +129,29 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H2">
         <v>81</v>
       </c>
       <c r="I2">
-        <v>81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CAA CELLS</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -179,17 +178,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">DUZENLE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -204,29 +203,29 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H4">
         <v>81</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE</t>
+          <t xml:space="preserve">ONGOING</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -241,29 +240,29 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H5">
         <v>81</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONGOING</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -278,29 +277,29 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>81</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">Unnamed box</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -315,49 +314,12 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>81</v>
       </c>
       <c r="I7">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not placed yet</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not placed yet</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unnamed box</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="E8">
-        <v>9</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>81</v>
-      </c>
-      <c r="I8">
         <v>81</v>
       </c>
     </row>
@@ -371,14 +333,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)  ·  baris  ·  0/81 full</t>
+          <t xml:space="preserve">UMUT CAA CELLS  ·  umut  ·  81/81 full</t>
         </is>
       </c>
     </row>
@@ -436,6 +398,51 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATP7B KO g3 p102</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATP7B KO g3 p99</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATP7B KO g3 p97</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK TOX4 OX p+12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK TOX4 OX p+3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK TOX4 OX p+3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK TOX4 OX p+4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK TOX4 OX p+4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR NT KO p?</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -443,6 +450,51 @@
           <t xml:space="preserve">B</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR TOX4 KO g1.2 p?</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 TOX4 KO g2.2 p?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 TOX4 KO g2.2 p?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR ATP7B KO p?</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR ATF3 KO p?</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1 p?</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR TOX4 KO g1.2 p?</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR TOX4 KO g2.2 p?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1 p?</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -450,6 +502,51 @@
           <t xml:space="preserve">C</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p50</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 TOX4 OX p+3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 CBX3 KO g2 p6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 CBX3 KO g1 p6</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p+2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p+2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p+2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 gNT p6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 HOXB6 KO g1 p6</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -457,6 +554,51 @@
           <t xml:space="preserve">D</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LCC-V p?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap V1G1 p+1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada CASPEX (no sort) p+20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap ER p</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada V1G1 p+2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canadaa V1G1 p+1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canadaa V1G1 p+1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+11</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada CASPEX (no sort) p+20</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -464,6 +606,51 @@
           <t xml:space="preserve">E</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR NT KO p?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR MTF1 KO p?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR ATP7B KO p?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR TOX4 KO g2.2 p?</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR MTF1 KO p?</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1 p?</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR ATF3 KO p?</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p+8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +658,51 @@
           <t xml:space="preserve">F</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p11</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p9</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p9</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p11</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p11</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP1 p20</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP1 p20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p11</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -478,6 +710,51 @@
           <t xml:space="preserve">G</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada CASPEX (no sort) p+20</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+6</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada V1G1 p+2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+15</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LCC-V 99.17% p?</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gNT p+21</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gP1 p+21</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -485,11 +762,101 @@
           <t xml:space="preserve">H</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK FOXA1 KO g2 p16</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK JUN1 KO g2 p13</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK RFX KO g2 p17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK FOXA1 KO g1 p17</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK HOXB6 KO g1 p18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK RFX KO g1 p17</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK SPEN KO g2 p14</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK HOXB6 KO g2 p18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK FOXA1 KO g1 p14</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK GATA6 KO g2 p18</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK NRF2 KO g1 p17</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK NRF2 KO g2 p17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK FOXA1 KO g2 p14</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK GATA6 KO g1 p18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK CBX3 KO G1 p15</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK POU3F3 KO g1 p15</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATP7B-GFP p47</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT (10) p15</t>
         </is>
       </c>
     </row>
@@ -503,14 +870,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CAA CELLS  ·  umut  ·  81/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -80  ·  umut  ·  81/81 full</t>
         </is>
       </c>
     </row>
@@ -570,47 +937,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3 p102</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1 p4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3 p99</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1 p4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3 p97</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX p+12</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT p+6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX p+3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT p+6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX p+3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX p+4</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3 p+7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX p+4</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1 p5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR NT KO p?</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+7</t>
         </is>
       </c>
     </row>
@@ -622,47 +989,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR TOX4 KO g1.2 p?</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1 p28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 TOX4 KO g2.2 p?</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1 p28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 TOX4 KO g2.2 p?</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 p28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR ATP7B KO p?</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 p28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR ATF3 KO p?</t>
+          <t xml:space="preserve">HEK JUN KO g1 p19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1 p?</t>
+          <t xml:space="preserve">HEK STAT1 KO g2 p30</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR TOX4 KO g1.2 p?</t>
+          <t xml:space="preserve">HEK STAT1 KO g1 p19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR TOX4 KO g2.2 p?</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2 p19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1 p?</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1 p19</t>
         </is>
       </c>
     </row>
@@ -674,47 +1041,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p50</t>
+          <t xml:space="preserve">HEK293T p14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 OX p+3</t>
+          <t xml:space="preserve">HEK293T p19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g2 p6</t>
+          <t xml:space="preserve">HEK APEX1 g1 p19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 KO g1 p6</t>
+          <t xml:space="preserve">HEK STAT1 KO g2 p28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p+2</t>
+          <t xml:space="preserve">HEK gNT(20) p13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p+2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1 p13</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p+2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 p13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT p6</t>
+          <t xml:space="preserve">HEK 3xFLAG p+6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 KO g1 p6</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2 p37</t>
         </is>
       </c>
     </row>
@@ -726,47 +1093,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V p?</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3 p+9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap V1G1 p+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1 p7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX (no sort) p+20</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p|+7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap ER p</t>
+          <t xml:space="preserve">Du145 p11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G1 p+2</t>
+          <t xml:space="preserve">Du145 p11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1 p+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p+9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1 p+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT p14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada p+11</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX (no sort) p+20</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3 p10</t>
         </is>
       </c>
     </row>
@@ -778,47 +1145,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR NT KO p?</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX p6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR MTF1 KO p?</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1 p6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR ATP7B KO p?</t>
+          <t xml:space="preserve">Huh7 CBX3 OX p6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR TOX4 KO g2.2 p?</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2 p6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR MTF1 KO p?</t>
+          <t xml:space="preserve">Huh7 TOX4 KO p+12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1 p?</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24 p82</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR ATF3 KO p?</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1 p?</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p+8</t>
+          <t xml:space="preserve">Huh7 ATP7B KO p81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24 p84</t>
         </is>
       </c>
     </row>
@@ -830,47 +1197,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR p11</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1 p48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR p9</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1 p48</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR p11</t>
+          <t xml:space="preserve">HEK gNT p22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR p9</t>
+          <t xml:space="preserve">HEK gNT p22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR p11</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2 p37</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR p11</t>
+          <t xml:space="preserve">HEK ATP7B KO g3 p+7</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1 p20</t>
+          <t xml:space="preserve">HEK TOX4 KO g2 p+6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1 p20</t>
+          <t xml:space="preserve">HEK TOX4 KO g2 p+7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR p11</t>
+          <t xml:space="preserve">HEK293T p19</t>
         </is>
       </c>
     </row>
@@ -882,47 +1249,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX (no sort) p+20</t>
+          <t xml:space="preserve">LNCX gNT p+20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada p+15</t>
+          <t xml:space="preserve">LNCX gNT p+20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada p+15</t>
+          <t xml:space="preserve">LNCX gP2 p+21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada p+6</t>
+          <t xml:space="preserve">LNCX gP2 p+20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G1 p+2</t>
+          <t xml:space="preserve">LnCap Canada V1G4 p41</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada p+15</t>
+          <t xml:space="preserve">LnCap Canada V1G3 p41</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V 99.17% p?</t>
+          <t xml:space="preserve">LnCap Canada V1G2 p41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT p+21</t>
+          <t xml:space="preserve">LnCapCASPEX no select E p45769</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1 p+21</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1 p?</t>
         </is>
       </c>
     </row>
@@ -934,47 +1301,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g2 p16</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1 p43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2 p13</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX p42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2 p17</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1 p43</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g1 p17</t>
+          <t xml:space="preserve">HEK ATP7B GFP p42</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1 p18</t>
+          <t xml:space="preserve">HEK ATP7B GFP p42</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1 p17</t>
+          <t xml:space="preserve">HEK CASPEX gNT p?</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2 p14</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX p42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2 p18</t>
+          <t xml:space="preserve">HEK APEX1 OX p21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g1 p14</t>
+          <t xml:space="preserve">HEK CBX3 OX p28</t>
         </is>
       </c>
     </row>
@@ -986,47 +1353,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2 p18</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1 p17</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2 p17</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g2 p14</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1 p18</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO G1 p15</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1 p15</t>
+          <t xml:space="preserve">Du145 p?</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B-GFP p47</t>
+          <t xml:space="preserve">DuPar50CR+1 p218</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10) p15</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3 p8</t>
         </is>
       </c>
     </row>
@@ -1040,14 +1407,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80  ·  umut  ·  81/81 full</t>
+          <t xml:space="preserve">DUZENLE  ·  umut  ·  74/81 full</t>
         </is>
       </c>
     </row>
@@ -1107,47 +1474,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1 p4</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1 p10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1 p4</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3 p10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1 p10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p+2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 p25</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 p25</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDtxR p14</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDtxR p14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p?</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT p+6</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT p+6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+5</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3 p+7</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1 p5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+7</t>
         </is>
       </c>
     </row>
@@ -1159,47 +1526,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1 p28</t>
+          <t xml:space="preserve">LnCapCASPEX no select p?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1 p28</t>
+          <t xml:space="preserve">LnCapCASPEX no select C p?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 p28</t>
+          <t xml:space="preserve">LnCapCASPEX no select E p?</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 p28</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2 p?</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1 p19</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2 p?</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2 p30</t>
+          <t xml:space="preserve">LnCapCASPEX no select H p?</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1 p19</t>
+          <t xml:space="preserve">LnCapCASPEX no select H p?</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2 p19</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1 p?</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1 p19</t>
+          <t xml:space="preserve">LCC-K no sort p?</t>
         </is>
       </c>
     </row>
@@ -1211,47 +1578,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T p14</t>
+          <t xml:space="preserve">LCC-I no sort p?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T p19</t>
+          <t xml:space="preserve">LCC-R no sort p?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1 p19</t>
+          <t xml:space="preserve">LCC-V no sort p?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2 p28</t>
+          <t xml:space="preserve">LCC-C* p?</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20) p13</t>
+          <t xml:space="preserve">LCC-H p?</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1 p13</t>
+          <t xml:space="preserve">LCC-E p?</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 p13</t>
+          <t xml:space="preserve">LCC-K p?</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG p+6</t>
+          <t xml:space="preserve">LCC-I p?</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2 p37</t>
+          <t xml:space="preserve">LCC-K p?</t>
         </is>
       </c>
     </row>
@@ -1263,47 +1630,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3 p+9</t>
+          <t xml:space="preserve">LCC-R p?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1 p7</t>
+          <t xml:space="preserve">LCC-I p?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p|+7</t>
+          <t xml:space="preserve">LCC-R p?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 p11</t>
+          <t xml:space="preserve">LnCap Canada V1G1 p?</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 p11</t>
+          <t xml:space="preserve">LnCap Canada V1G1 p?</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p+9</t>
+          <t xml:space="preserve">LnCap Canada V1G1 p?</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT p14</t>
+          <t xml:space="preserve">LnCap Canada V1G1 p?</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+12</t>
+          <t xml:space="preserve">LNCX p+21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3 p10</t>
+          <t xml:space="preserve">LNCX p+21</t>
         </is>
       </c>
     </row>
@@ -1315,47 +1682,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX p6</t>
+          <t xml:space="preserve">Huh7 POU3F2 KO g1 p?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1 p6</t>
+          <t xml:space="preserve">Huh7 TOX4 KO p+15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX p6</t>
+          <t xml:space="preserve">Huh7 TOX4 KO p+14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2 p6</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep2 p13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO p+12</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24 p82</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1 p?</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 ATP7B KO p81</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24 p84</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep2 p14</t>
         </is>
       </c>
     </row>
@@ -1367,47 +1714,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1 p48</t>
+          <t xml:space="preserve">HEK TOX4 KO g2 p+9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1 p48</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 p40</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT p22</t>
+          <t xml:space="preserve">HEK APEX1 KO g2 p22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT p22</t>
+          <t xml:space="preserve">HEK ATP7B-GFP p30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2 p37</t>
+          <t xml:space="preserve">HEK JUN KO g2 p18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3 p+7</t>
+          <t xml:space="preserve">HEK E2F1 sh2 p20</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2 p+6</t>
+          <t xml:space="preserve">HEK ATP7B-GFP p30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2 p+7</t>
+          <t xml:space="preserve">HEK E2F1 sh2 p20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T p19</t>
+          <t xml:space="preserve">HEK ATP7B-GFP p30</t>
         </is>
       </c>
     </row>
@@ -1419,47 +1766,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT p+20</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use) p+11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT p+20</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use) p+11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2 p+21</t>
+          <t xml:space="preserve">LnCap Canada p+9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2 p+20</t>
+          <t xml:space="preserve">LnCap Canada p+9</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4 p41</t>
+          <t xml:space="preserve">LNCX p+21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3 p41</t>
+          <t xml:space="preserve">LNCX p+21</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2 p41</t>
+          <t xml:space="preserve">LNCX gP1 p+24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E p45769</t>
+          <t xml:space="preserve">LNCX gP2 p+25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1 p?</t>
+          <t xml:space="preserve">LNCX gP2 p+25</t>
         </is>
       </c>
     </row>
@@ -1471,47 +1818,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1 p43</t>
+          <t xml:space="preserve">LuCap35CR p11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX p42</t>
+          <t xml:space="preserve">LUCX p15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1 p43</t>
+          <t xml:space="preserve">LUCX p15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP p42</t>
+          <t xml:space="preserve">LUCX p17</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP p42</t>
+          <t xml:space="preserve">LUCX p17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT p?</t>
+          <t xml:space="preserve">LUCX p17</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX p42</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK APEX1 OX p21</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK CBX3 OX p28</t>
+          <t xml:space="preserve">LUCX p19</t>
         </is>
       </c>
     </row>
@@ -1523,47 +1860,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+3</t>
+          <t xml:space="preserve">HEK E2F1 sh1 p20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+4</t>
+          <t xml:space="preserve">HEK ATP7B-GFP p31</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+4</t>
+          <t xml:space="preserve">HEK E2F1 sh1 p20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+4</t>
+          <t xml:space="preserve">HEK ATP7B-GFP p31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+4</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP p42</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 p+4</t>
+          <t xml:space="preserve">HEK ATP7B KO g3 p+2</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 p?</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPar50CR+1 p218</t>
+          <t xml:space="preserve">HEK ATP7B KO g3 p+2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3 p8</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2 p24</t>
         </is>
       </c>
     </row>
@@ -1577,14 +1909,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE  ·  umut  ·  74/81 full</t>
+          <t xml:space="preserve">ONGOING  ·  umut  ·  76/81 full</t>
         </is>
       </c>
     </row>
@@ -1644,47 +1976,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1 p10</t>
+          <t xml:space="preserve">LNCX p+22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3 p10</t>
+          <t xml:space="preserve">LCC-V 99.17% p+4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1 p10</t>
+          <t xml:space="preserve">LnCap478 #2 98% p28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p+2</t>
+          <t xml:space="preserve">LnCap Canada p+7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 p25</t>
+          <t xml:space="preserve">LnCap (m3) no sort p+14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 p25</t>
+          <t xml:space="preserve">LnCap Canada p+14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR p14</t>
+          <t xml:space="preserve">LnCap (m3) (sortER) p+13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR p14</t>
+          <t xml:space="preserve">LnCap (m3) (sortER) p+13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2 p?</t>
+          <t xml:space="preserve">LnCap Canada p+14</t>
         </is>
       </c>
     </row>
@@ -1696,47 +2028,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select p?</t>
+          <t xml:space="preserve">HEK TOX4 OX 3xFLAG p2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select C p?</t>
+          <t xml:space="preserve">HEK293T p7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E p?</t>
+          <t xml:space="preserve">HEK gNT(20) p16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2 p?</t>
+          <t xml:space="preserve">HEK ATF3 KO 20 p18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2 p?</t>
+          <t xml:space="preserve">HEK 3xFLAG p+7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H p?</t>
+          <t xml:space="preserve">HEK HOXB6 OX p36</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H p?</t>
+          <t xml:space="preserve">HEK lef1 OX p?</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1 p?</t>
+          <t xml:space="preserve">HEK ATF3 OX p?</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-K no sort p?</t>
+          <t xml:space="preserve">HEK ATP7B KO g3 p+13</t>
         </is>
       </c>
     </row>
@@ -1748,47 +2080,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-I no sort p?</t>
+          <t xml:space="preserve">Huh7 lef1 OX p?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-R no sort p?</t>
+          <t xml:space="preserve">Huh7 3xFLAG p?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V no sort p?</t>
+          <t xml:space="preserve">Huh7 CASPEX gNT p?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-C* p?</t>
+          <t xml:space="preserve">Huh7 ATF3 KO20 p6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-H p?</t>
+          <t xml:space="preserve">Huh7 ATF3 OX20r1 p6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-E p?</t>
+          <t xml:space="preserve">Huh7 ATF3KO10 p7</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-K p?</t>
+          <t xml:space="preserve">Huh7 p51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-I p?</t>
+          <t xml:space="preserve">Huh7 p51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-K p?</t>
+          <t xml:space="preserve">Huh7 p42</t>
         </is>
       </c>
     </row>
@@ -1800,47 +2132,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-R p?</t>
+          <t xml:space="preserve">HEK HOXB6 OX p36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-I p?</t>
+          <t xml:space="preserve">HEK ATF3 OX10r1 p18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-R p?</t>
+          <t xml:space="preserve">HEK ATP7B KO-1 p11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G1 p?</t>
+          <t xml:space="preserve">HEK ATP7B KO-2 p11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G1 p?</t>
+          <t xml:space="preserve">HEK ATP7B KO-3 p11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G1 p?</t>
+          <t xml:space="preserve">HEK ATP7B GFP p53</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G1 p?</t>
+          <t xml:space="preserve">HEK ATF3 KO10 p9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX p+21</t>
+          <t xml:space="preserve">HEK CASPEX Single p+6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX p+21</t>
+          <t xml:space="preserve">HEK CASPEX Single p+6</t>
         </is>
       </c>
     </row>
@@ -1852,27 +2184,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F2 KO g1 p?</t>
+          <t xml:space="preserve">HepG2 p+2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO p+15</t>
+          <t xml:space="preserve">HepG2 p+2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO p+14</t>
+          <t xml:space="preserve">HepG2 p+5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep2 p13</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep2 p14</t>
+          <t xml:space="preserve">HepG2 p7</t>
         </is>
       </c>
     </row>
@@ -1884,47 +2211,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2 p+9</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT p?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 p40</t>
+          <t xml:space="preserve">Du145 p14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2 p22</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2 p14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B-GFP p30</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2 p14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g2 p18</t>
+          <t xml:space="preserve">Du145 p?</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh2 p20</t>
+          <t xml:space="preserve">Du145 p?</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B-GFP p30</t>
+          <t xml:space="preserve">Du145 p?</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh2 p20</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1 p15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B-GFP p30</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT p+3</t>
         </is>
       </c>
     </row>
@@ -1936,47 +2263,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use) p+11</t>
+          <t xml:space="preserve">LnCap Canada p+23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use) p+11</t>
+          <t xml:space="preserve">LNCAP BMK p?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada p+9</t>
+          <t xml:space="preserve">LnCap Canada p+17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada p+9</t>
+          <t xml:space="preserve">LnCap Canada p+17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX p+21</t>
+          <t xml:space="preserve">LnCap Canada p+17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX p+21</t>
+          <t xml:space="preserve">LnCap Canada p+17</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1 p+24</t>
+          <t xml:space="preserve">LNC478 #2 98% p24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2 p+25</t>
+          <t xml:space="preserve">LNC478 #1 p23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2 p+25</t>
+          <t xml:space="preserve">LNC478 #3 p23</t>
         </is>
       </c>
     </row>
@@ -1988,37 +2315,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t xml:space="preserve">LuCap35CR p9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap (m1) no sort p10</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p10</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t xml:space="preserve">LuCap35CR p11</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUCX p15</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUCX p15</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUCX p17</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX p17</t>
+          <t xml:space="preserve">LuCap35CR p11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX p17</t>
+          <t xml:space="preserve">LUCX gP2 p20</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX p19</t>
+          <t xml:space="preserve">LUCX gP1 p20</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP1 p20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP2 p20</t>
         </is>
       </c>
     </row>
@@ -2030,42 +2367,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh1 p20</t>
+          <t xml:space="preserve">LnCap Canada p+14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B-GFP p31</t>
+          <t xml:space="preserve">LNCX p12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh1 p20</t>
+          <t xml:space="preserve">LNCX p+17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B-GFP p31</t>
+          <t xml:space="preserve">LNCX p+17</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP p42</t>
+          <t xml:space="preserve">LnCap Canada p+14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3 p+2</t>
+          <t xml:space="preserve">LnCap Canada p+14</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3 p+2</t>
+          <t xml:space="preserve">LNCX gNT p+24</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gP2 p+24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2 p24</t>
+          <t xml:space="preserve">LNCX gP1 p+24</t>
         </is>
       </c>
     </row>
@@ -2079,14 +2421,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONGOING  ·  umut  ·  76/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  30/81 full</t>
         </is>
       </c>
     </row>
@@ -2146,47 +2488,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX p+22</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1 p18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V 99.17% p+4</t>
+          <t xml:space="preserve">HEK ATF3OX10r1 p6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap478 #2 98% p28</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap Canada p+7</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap (m3) no sort p+14</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap Canada p+14</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap (m3) (sortER) p+13</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap (m3) (sortER) p+13</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap Canada p+14</t>
+          <t xml:space="preserve">HEK gNT p27</t>
         </is>
       </c>
     </row>
@@ -2198,47 +2510,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX 3xFLAG p2</t>
+          <t xml:space="preserve">HEK293T p14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T p7</t>
+          <t xml:space="preserve">HEK293T p14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20) p16</t>
+          <t xml:space="preserve">HEK293T p21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20 p18</t>
+          <t xml:space="preserve">HEK293T p16</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG p+7</t>
+          <t xml:space="preserve">HEK293T p13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 OX p36</t>
+          <t xml:space="preserve">HEK293T p16</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK lef1 OX p?</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATF3 OX p?</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATP7B KO g3 p+13</t>
+          <t xml:space="preserve">HEK293T p14</t>
         </is>
       </c>
     </row>
@@ -2250,47 +2552,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 lef1 OX p?</t>
+          <t xml:space="preserve">Du145 p10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG p?</t>
+          <t xml:space="preserve">Du145 p10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CASPEX gNT p?</t>
+          <t xml:space="preserve">Du145 p10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO20 p6</t>
+          <t xml:space="preserve">Du145 p10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX20r1 p6</t>
+          <t xml:space="preserve">Du145 p11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3KO10 p7</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT p+3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p51</t>
+          <t xml:space="preserve">Du145 p11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p51</t>
+          <t xml:space="preserve">Du145 p11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p42</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3 p15</t>
         </is>
       </c>
     </row>
@@ -2302,47 +2604,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 OX p36</t>
+          <t xml:space="preserve">Huh7 p51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX10r1 p18</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATP7B KO-1 p11</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATP7B KO-2 p11</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATP7B KO-3 p11</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATP7B GFP p53</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATF3 KO10 p9</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK CASPEX Single p+6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK CASPEX Single p+6</t>
+          <t xml:space="preserve">Huh7 p15</t>
         </is>
       </c>
     </row>
@@ -2354,22 +2621,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2 p+2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 p?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2 p+2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3 p15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2 p+5</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1 p15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2 p7</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski) p?</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski) p?</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski) p?</t>
         </is>
       </c>
     </row>
@@ -2381,47 +2658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT p?</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10 p10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 p14</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2 p14</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2 p14</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p?</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p?</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p?</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1 p15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT p+3</t>
+          <t xml:space="preserve">MDA-MB gNT p10</t>
         </is>
       </c>
     </row>
@@ -2433,47 +2675,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada p+23</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNCAP BMK p?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap Canada p+17</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap Canada p+17</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap Canada p+17</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap Canada p+17</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNC478 #2 98% p24</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNC478 #1 p23</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNC478 #3 p23</t>
+          <t xml:space="preserve">LNCX p19</t>
         </is>
       </c>
     </row>
@@ -2483,101 +2685,11 @@
           <t xml:space="preserve">H</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LuCap35CR p9</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LuCap (m1) no sort p10</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LuCap35CR p10</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LuCap35CR p11</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LuCap35CR p11</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUCX gP2 p20</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUCX gP1 p20</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUCX gP1 p20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUCX gP2 p20</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap Canada p+14</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNCX p12</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNCX p+17</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNCX p+17</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap Canada p+14</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap Canada p+14</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNCX gNT p+24</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNCX gP2 p+24</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNCX gP1 p+24</t>
         </is>
       </c>
     </row>
@@ -2591,14 +2703,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  30/81 full</t>
+          <t xml:space="preserve">Unnamed box  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -2656,288 +2768,6 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1 p18</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATF3OX10r1 p6</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK gNT p27</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T p14</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T p14</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T p21</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T p16</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T p13</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T p16</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T p14</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p10</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p10</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p10</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p11</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT p+3</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p11</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p11</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3 p15</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 p51</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 p15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 p?</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3 p15</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1 p15</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski) p?</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski) p?</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski) p?</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10 p10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MDA-MB gNT p10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LNCX p19</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not placed yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unnamed box  ·  umut  ·  0/81 full</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -203,13 +203,13 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H4">
         <v>81</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -277,13 +277,13 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>81</v>
       </c>
       <c r="I6">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -1414,7 +1414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE  ·  umut  ·  74/81 full</t>
+          <t xml:space="preserve">DUZENLE  ·  umut  ·  78/81 full</t>
         </is>
       </c>
     </row>
@@ -1703,6 +1703,26 @@
       <c r="F9" t="inlineStr">
         <is>
           <t xml:space="preserve">Huh7 ATF3 OX rep2 p14</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 gNT p17</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 gNT p17</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3 p18</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3 p18</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  30/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  42/81 full</t>
         </is>
       </c>
     </row>
@@ -2501,6 +2521,36 @@
           <t xml:space="preserve">HEK gNT p27</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek atf3 ko rep2 p21</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek atf3 ko rep2 p21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 3xflag p21</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 3xflag p21</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek atf3 ox rep3 p28</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek atf3 ox rep3 p28</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2543,6 +2593,16 @@
           <t xml:space="preserve">HEK293T p14</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek gnt p21</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek gnt p21</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2610,6 +2670,26 @@
       <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">Huh7 p15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 3xFLAG p17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 3xFLAG p17</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3 p18</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3 p18</t>
         </is>
       </c>
     </row>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -9,6 +9,17 @@
     <sheet name="ONGOING" sheetId="5" r:id="rId5"/>
     <sheet name="UMUT CELLS -4-" sheetId="6" r:id="rId6"/>
     <sheet name="Unnamed box" sheetId="7" r:id="rId7"/>
+    <sheet name="-80 Box1" sheetId="8" r:id="rId8"/>
+    <sheet name="-80 Box2" sheetId="9" r:id="rId9"/>
+    <sheet name="-80 Box3" sheetId="10" r:id="rId10"/>
+    <sheet name="-80 Box4" sheetId="11" r:id="rId11"/>
+    <sheet name="-80 Box5" sheetId="12" r:id="rId12"/>
+    <sheet name="-80 Box6" sheetId="13" r:id="rId13"/>
+    <sheet name="LiqNitro 1" sheetId="14" r:id="rId14"/>
+    <sheet name="LiqNitro 2" sheetId="15" r:id="rId15"/>
+    <sheet name="Beyza Caa Hücre Box 1" sheetId="16" r:id="rId16"/>
+    <sheet name="Beyza Caa Sıvı Azot Box 1" sheetId="17" r:id="rId17"/>
+    <sheet name="Beyza Caa Hücre Box 2" sheetId="18" r:id="rId18"/>
   </sheets>
 </workbook>
 </file>
@@ -203,13 +214,13 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H4">
         <v>81</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -277,13 +288,13 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H6">
         <v>81</v>
       </c>
       <c r="I6">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -314,13 +325,4658 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>81</v>
       </c>
       <c r="I7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baris</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
         <v>81</v>
+      </c>
+      <c r="I8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baris</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>9</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>54</v>
+      </c>
+      <c r="H9">
+        <v>81</v>
+      </c>
+      <c r="I9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baris</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>79</v>
+      </c>
+      <c r="H10">
+        <v>81</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baris</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>9</v>
+      </c>
+      <c r="F11">
+        <v>9</v>
+      </c>
+      <c r="G11">
+        <v>73</v>
+      </c>
+      <c r="H11">
+        <v>81</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baris</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>69</v>
+      </c>
+      <c r="H12">
+        <v>81</v>
+      </c>
+      <c r="I12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box6</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baris</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+      <c r="G13">
+        <v>76</v>
+      </c>
+      <c r="H13">
+        <v>81</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LiqNitro 1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baris</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>9</v>
+      </c>
+      <c r="F14">
+        <v>9</v>
+      </c>
+      <c r="G14">
+        <v>63</v>
+      </c>
+      <c r="H14">
+        <v>81</v>
+      </c>
+      <c r="I14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LiqNitro 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">baris</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>9</v>
+      </c>
+      <c r="F15">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>75</v>
+      </c>
+      <c r="H15">
+        <v>81</v>
+      </c>
+      <c r="I15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beyzat</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>81</v>
+      </c>
+      <c r="H16">
+        <v>81</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beyzat</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>9</v>
+      </c>
+      <c r="F17">
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <v>24</v>
+      </c>
+      <c r="H17">
+        <v>81</v>
+      </c>
+      <c r="I17">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beyzat</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>70</v>
+      </c>
+      <c r="H18">
+        <v>81</v>
+      </c>
+      <c r="I18">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box3  ·  baris  ·  79/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR fluc-mCherry SORTED 28.04.21 BARO -</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22DoceR flucmCherry SORTED 28.04.21 BARO -</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22CabaR flucmCherry SORTED 28.04.21 BARO -</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR flucmCherry SORTED 28.04.21 BARO -</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR SIRT1 28.04.21 BARO -</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR SIRT1 28.04.21 BARO -</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 SIRT1 (retro) P81 29.03.21 BARO 81.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HeLa P31 29.03.21 BARO 31.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145-Ki PC P81 11.06.21 BARO 81.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #10 P19+10 07.06.21 19+10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #1 P19+10 07.06.21 19+10</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #3 P19+10 07.06.21 19+10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #12 P19+10 07.06.21 19+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #9 P19+10 07.06.21 19+10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-10CR P106 13.07.21 106.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-10CR P106 13.07.21 106.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P24 26.12.19 24.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-8CR P99 13.07.21 99.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P24 26.12.19 24.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-50CR P134 08.04.22 134.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-8CR P99 13.07.21 99.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P84 12.07.21 BARO 84.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P40 29.04.22 BARO 40.0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P45 04.10.21 BARO 45.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-CR 1x15uM recovered P110 19.08.21 BARO 110.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-1x15CR P111 19.08.21 111.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2x15CR P112 13.09.21 112.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR p134 15.04.22 134.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #11 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #31 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #32 18.07.21 -</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #20 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #25 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #24 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #18 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #22 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #13 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #3 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #5 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #8 18.07.21 -</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #9 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #1 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #26 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #29 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #21 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #34 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #4 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du-Ki #10 18.07.21 -</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-50CR P134 08.04.22 BARO 134.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2x20CR P130 25.02.22 BARO 130.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSCC40 P39 15.02.22 BARO 39.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSCC40 P39 15.02.22 BARO 39.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCaP P15-Canada 14.10.21 BARO 15.0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-1x25CR P122 30.03.22 BARO 122.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HepG2 PX+11 02.10.21 BARO X+11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 P32 23.10.21 BARO 32.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-15CR* P122 16.12.21 BARO 122.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-luc 30.03.22 Ayça -</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 P32 23.10.21 BARO 32.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DtxR-luc 30.03.22 Ayça -</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PC3 cell pellet -</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PC3 cell pellet -</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCaP pellet -</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCaP pellet -</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U2OS pellet -</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 pellet -</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 pellet -</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HepG2 pellet -</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MDA-231 pellet -</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box4  ·  baris  ·  73/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P134 17.06.22 BARO 134.0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR P56 07.08.20 BARO 56.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR P56 07.08.20 BARO 56.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+3 P142 22.06.22 BARO 142.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+3 P142 22.06.22 BARO 142.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+2 P140 17.06.22 BARO 140.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR P56 07.08.20 BARO 56.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P134 17.06.22 BARO 134.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-50CR+1 P138 24.06.22 BARO 138.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-1x50CR P129 08.02.22 BARO 129.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-15CR P118 08.02.22 BARO 118.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-25CR P130 08.02.22 BARO 130.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P82 16.06.21 BARO 82.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P38 29.06.22 BARO 38.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+2 P140 17.06.22 BARO 140.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+2 P140 17.06.22 BARO 140.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #10 21.08.21 BARO -</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P84 12.07.21 BARO 84.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PC3 P26 (MF) 28.10.21 BARO 26.0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCaP P17 (MF) 28.10.21 BARO 17.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PC3 P26 (MF) 28.10.21 BARO 26.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U2OS P13 04.09.20 BARO 13.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RPE1 P36 12.10.21 BARO 36.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P51 23.10.21 BARO 51.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H1299 12.10.21 BARO -</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RPE1 P35 12.10.21 BARO 35.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RPE1 P35 12.10.21 BARO 35.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P136 24.6.22 136.0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-1x40CR P132 24.6.22 BARO 132.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuoOceR-1x40CR P132 24.6.22 BARO 132.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-50CR+1 P138 24.06.22 BARO 138.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P136 24.6.22 136.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR- flucmCherry SORTED 21.6.21 BARO -</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 fluc Ki PC P82 16.6.21 BARO 82.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR flucmCherry SORTED 21.6.21 BARO -</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIA-Paca2 16.6.21 BARO -</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSCC40 P42 04.03.22 Ayça 42.0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2x25CR P130 25.2.22 BARO 130.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR P149 17.12.22 BARO 149.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BT549 P5 21.11.22 BARO 5.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh3 17.10.22 BARO 50.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P5 1.3.22 BARO 5.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-40CR P140 11.09.22 BARO 140.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A549 P15 21.11.22 BARO 15.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2x50CR P143 14.10.22 BARO 143.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A549 P11 9.11.22 BARO 11.0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A549 P12 3.11.22 BARO 12.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P5 1.3.22 BARO 5.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BT549 P4 18.11.22 BARO 4.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-40CR P139 2.09.22 BARO 139.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-40CR P138 26.08.22 BARO 138.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #2 P46 13.12.22 BARO 46.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #11 P46 13.12.22 BARO 46.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #19 P46 13.12.22 BARO 46.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 PRMT6 sh1 14.10.22 BARO 50.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #27 P46 13.12.22 BARO 46.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #12 P46 13.12.22 BARO 46.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-40CR P140 11.09.22 BARO 140.0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-25CR P129 17.5.22 Ayça 129.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-1x50CR P142 28.9.22 BARO 142.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A549 P12 9.11.22 BARO 12.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh3 13.10.22 BARO 50.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 PRMT6 sh3 17.10.22 BARO 50.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 P60 9.11.22 BARO 60.0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-PARc P128 13.12.22 BARO 128.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A549 P14 18.11.22 BARO 14.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDOceR-50CR P149 17.12.22 BARO 149.0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+4 P148 5.8.22 BARO 148.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR P148 9.12.22 BARO 148.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-30CR P154 18.11.22 BARO 154.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hek-Ki #5 B.Altay 11.8.22 -</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hek-Ki #6 B.Altay 11.8.22 -</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hek-Ki #8 B.Altay 11.8.22 -</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box5  ·  baris  ·  69/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P6 29.12.22 BARO 6.0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-50CR+2 P142 6.1.23 BARO 142.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-flucmCherry 14.7.21 BARO -</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh2 (1) 10.3.23 BARO 34.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh3 (1) 10.3.23 BARO 34.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh1 (2) 10.3.23 BARO 34.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh3 (2) 10.3.23 BARO 34.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P28 17.2.23 BARO 28.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-BCHE sh2 1.3.23 BARO -</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-30CR P162 6.3.23 BARO 162.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P39 shGFP 21.2.23 BARO 39.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-BCHE sh5 1.3.23 BARO -</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 -Ki 2nd sorted P93 no puro 24.5.21 BARO 93.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-flucmCherry 14.7.21 BARO -</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-flucmCherry 14.7.21 BARO -</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P6 29.12.22 BARO 6.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P29 2.1.23 BARO 29.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P130 3.2.23 BARO 130.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P126 29.12.22 BARO 126.0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #17 P46 26.12.22 BARO 46.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P39 shGFP 21.2.23 BARO 39.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-PARc P135 26.1.23 BARO 135.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #8 P46 26.12.22 BARO 46.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P39 1.2.23 BARO 39.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-BCHE sh5 1.3.23 BARO -</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P28 17.2.23 BARO 28.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh2 (2) 10.3.23 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+7 P169 20.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #10 P46 26.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P121 29.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P6 29.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-flucmCherry 14.7.21 BARO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P127 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P30 5.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P119 22.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #13 P46 26.12.22 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P30 5.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-25CR P131 3.2.23 BARO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P132 26.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-50CR+2 P144 19.1.23</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P128 9.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 P60 9.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P128 26.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P61 21.2.23 BARO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P131 7.2.23 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh1 (1) 10.3.23 BARO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-BCHE sh2 1.3.23 BARO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDOceR-50CR+1 P150 6.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P56 31.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P132 26.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P61 21.2.23 BARO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P55 26.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P128 26.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR+1 P149 22.12.22 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A375 P19 7.2.23 İpek</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-50CR+2 P147 7.2.23 BARO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR+2 P153 7.2.23 BARO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-1x40CR P160 7.2.23 BARO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 (2) P36 7.2.23 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P128 26.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P55 26.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR+1 P153 26.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR+1 P153 26.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-50CR+2 P144 26.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR+1 P153 26.1.23 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box6  ·  baris  ·  76/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U87MG P5 İpek 27.09.18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P10 27.10.20 Can</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-PARc P134 19.91.23 BARO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #6 P19+10 7.6.21 BARO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #5 15.4.22 Ayça</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 NT virus P33 25.02.22 BARO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDOceR-PARc P129 12.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-50CR+2 P143 12.1.23 BARO (T25'e aç)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR+1 P151 12.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MCF7 P9 18.11.22 Büşra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 PRMT1KO virus P31 selected 15.2.22 BARO (Yağmur'dan virüs)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-50CR+2 P144 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P53 tet-PRMT1 sh2 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P53 tet-PRMT1 sh2 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-PARc P134 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+7 P168 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 PC P34 1.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+7 P168 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+7 P168 19.1.23 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P46 ATP7B/KO-g3 #23 20.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR P145 18.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P14 21.11.21 BARO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+6 P158 14.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh1 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #7 P46 20.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P11 (MF) 10.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+5 P153 11.9.22 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR P145 18.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-40CR P139 2.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P14 21.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A549 P12 3.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-1x30CR P148 11.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P81 1.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P5 1.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P40 (MF) 11.09.22 BARO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDOceR-50CR P145 18.11.22 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-flucmCherry SORTED 22.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 PRMT6 sh3 14.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR 1x30CR P147 2.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+5 P153 11.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR P137 17.5.22 BARO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 P15 29.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P10 MF 29.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 NT virus P31 selected 15.2.22 BARO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P83 1.3.22 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 P18 21.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-flucmCherry SORTED 22.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P13 18.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+4 P148 26.8.22 BARO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh2 17.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 PRMT6 sh1 17.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIAPAca2 P16 29.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2x40CR P137 5.8.22 BARO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-1x30CR P147 2.9.22 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 P14 1.7.22 BARO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2x30CR P152 3.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-30CR P154 18.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR P132 22.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-40CR P140 11.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P46 ATP7B/KO-g3 PC 9.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P18 1.7.22 BARO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2x50CR P131 4.3.22 Baltay</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh1 17.10.22 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #6 P46 13.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P11 (MF) 10.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #5 P46 13.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2.5CR P83 1.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #26 P46 26.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #14 P46 26.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #15 P46 26.12.22 BARO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LiqNitro 1  ·  baris  ·  63/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #9 P19+10 7.6.21 BARO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-flucmCherry SORTED 20.4.21</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #9 15.3.21</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #1 15.3.21</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.1.21 BARO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-PARc P75 26.11.21 BARO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-15CR P130 1.2.22 BARO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-8CR P99 1.2.22 BARO</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-25CR P130 1.2.22 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P78 29.11.21 BARO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2.5CR P75 29.11.21 BARO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P85 5.1.22 BARO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-15CR* P121 8.12.21 BARO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-10CR P110 13.7.21 BARO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-15CR P122 16.12.21 BARO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-15CR P121 8.12.21 BARO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR reminded P75 3.12.21 BARO</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-10CR P110 13.7.21 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-15CR P117 1.2.22 BARO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-25CR P124 16.12.21 BARO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-15CR P121 8.12.21 BARO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-10CR P112 1.2.22 BARO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-10CR P106 1.2.22 BARO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P74 29.11.21 BARO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-15CR P122 16.12.21 BARO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-1.5CR P62 1.10.20 BARO</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P61 25.9.20 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR P56 7.8.20 BARO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #3 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #10 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #12 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #9 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #1 P19+10 7.6.21 BARO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #3 P19+10 7.6.21 BARO</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-flucmCherry 15.3.21 BARO (flucmCherry üretilen HEK'ler)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 20.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-1.5CR P60 21.9.20 BARO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P61 25.9.20 BARO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #3 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #12 P19+10 7.6.21 BARO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #12 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22CabaR-flucmCherry SORTED 22.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-1.5CR P62 1.10.20 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22DoceR-flucmCherry SORTED 22.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P61 25.9.20 BARO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR-flucmCherry SORTED 20.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22DoceR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #1 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MCF7 P3 7.11.20 BARO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MDA-MB-231 (MF) P8 7.11.20 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P62 1.10.20 BARO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR-flucmCherry SORTED 20.04.21 BARO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-flucmCherry 15.3.21 BARO (flucmCherry üretilen HEK'ler)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P60 21.9.20 BARO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 20.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #10 P19+10 7.6.21 BARO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RPE P35 12.1.21 BARO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H1299 20.10.20 BARO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LiqNitro 2  ·  baris  ·  75/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-5CR P89 18.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P77 (FBS backup) 2.2.21 BARO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P77 (FBS backup) 2.2.21 BARO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-PARc of 2.5CR P74 17.2.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-10CR P103 28.6.21</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-10CR P105 7.7.21</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-10CR P103 28.6.21</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-PARc P86 21.6.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P82 7.7.21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-8CR P98 7.7.21</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-8CR P96 8.6.21</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-1x8CR P88 28.4.21</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-5CR P73 27.1.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-1.5CR P60 21.9.20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P64 12.1.21</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2.5CR P74 (FBS backup) 2.2.21</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P64 2.1.21</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2.5CR P74 (FBS backup) 2.2.21</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P64 12.1.21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P64 12.1.21</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-1x10CR P99 28.4.21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-5CR P92 18.3.21</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P77 21.6.21</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P65 26.3.21</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-10CR P105 19.6.21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-10CR P109 7.7.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-1.5CR P62 1.10.20</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-PARc P90 7.7.21</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-1.5CR P62 1.10.20</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-5CR P92 18.3.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-5CR P92 18.3.21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P62 1.10.20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P61 25.9.20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P81 (FBS backup) 2.2.21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 shGFP puro 51.0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSC19 TMEM16 OX p+17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSC19 Empty Vector P+18</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR PARc 137.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR PARc 137.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 shGFP hygro 200 ul 42.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 tet PRMT1 sh2(2) puro 49.0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #6 41.0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #6 41.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #5 31.0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #5 31.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #5 29.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #5 29.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #5 40.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1  ·  beyzat  ·  81/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 10.0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 16.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 16.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os 17.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hn30 20.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fadu 19.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hn30 20.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hn30 11.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 21.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fadu 19.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fadu 11.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u373 21.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fadu 19.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hn30 20.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os 17.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mpg ox 5.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda mpg ox 9.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda mpg ox 8.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os mpg ox 8.0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mpg ox 7.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mpg ox 7.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os mpg ox 8.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mpg ox 7.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda mpg ox 8.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os mpg ox 8.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda mpg ox 8.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os mpg ox 8.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox nek2 10.0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 3.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ko b9</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 k37r 16.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ko b5 2.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 k37r 2.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 k37r 16.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ko b9 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 3.0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 9.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 3.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox nek2 8.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox sh nek2 4.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox nek2 8.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox nek2 10.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 7.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 11.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 11.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ox</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ox 200 13.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ox 50 17.0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ox 100 17.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 sh elk1 100 14.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 sh elf1 100 20.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 shgfp 100 24.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 sh creb1 100 24.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 sh klf4 100 24.0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 sh elf1 100 24.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ox 200 19.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 sh klf4 200 20.0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 sh elk1 100 20.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 sh creb1 100 20.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cal27 shgfp 100 20.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 5 33.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 43.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek gnt 7.0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 mtf1 ox 24.0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 55.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 54.0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 6 43.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 48.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 5 39.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 43.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 6 49.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1  ·  beyzat  ·  24/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 4.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 5.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 k37r 7.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 k37r 2.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ko b5 7.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os nek2 ko b5 2.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 8.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 7.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 8.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda 3.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ox 200 21.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ox 200 19.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ox 200 23.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 6 43.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 5 34.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 mtf1 ox 31.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 mtf1 ox 29.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ko g3 c3 7.0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek gnt 5.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ko g3 c3 7.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 mtf1 ox 29.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek gnt 5.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mtf1 ko g3 c3 9.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2  ·  beyzat  ·  70/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 44.0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 44.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 45.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 45.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 6 45.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 6 45.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 6 46.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 6 45.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda mpg ox</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 5 34.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 5 34.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 5 34.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 5 34.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 23.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 23.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 23.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda mpg ox 12.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda mpg ox 12.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 7.0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 7.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 7.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 7.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 7.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 7.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 7.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda mpg ox 12.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox mpg 3 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 8.0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 8.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 8.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 8.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 8.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda nek2 ox 8.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox mpg 3 4.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox mpg 3 4.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox mpg 3 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox mpg 1 4.0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox mpg 1 4.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox mpg 1 4.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mpg ox 14.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek mpg ox 14.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek apex1 ox 21.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox nek2 ox 12.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek nek2 ox 29.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 19.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek apex1 ox 16.0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek shgfp 16.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda 29.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox mpg 7.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox mpg 7.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda dox mpg 21.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek dox mpg 14.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mda shgfp 25.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek shgfp 15.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox sh nek2 11.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u2os dox nek2 16.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 18.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 18.0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 16.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 18.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 16.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 10.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 18.0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 17.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 18.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 18.0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 18.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 18.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek 18.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1284,7 +5940,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E p45769</t>
+          <t xml:space="preserve">LnCapCASPEX no select E p?</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1388,7 +6044,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1 p218</t>
+          <t xml:space="preserve">DuPar50CR+1 P218</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1414,7 +6070,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE  ·  umut  ·  78/81 full</t>
+          <t xml:space="preserve">DUZENLE  ·  umut  ·  76/81 full</t>
         </is>
       </c>
     </row>
@@ -1705,19 +6361,9 @@
           <t xml:space="preserve">Huh7 ATF3 OX rep2 p14</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">Huh7 gNT p17</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 gNT p17</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3 p18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2448,7 +7094,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  42/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  36/81 full</t>
         </is>
       </c>
     </row>
@@ -2521,29 +7167,14 @@
           <t xml:space="preserve">HEK gNT p27</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek atf3 ko rep2 p21</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ko rep2 p21</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek 3xflag p21</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2 p21</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek 3xflag p21</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek atf3 ox rep3 p28</t>
+          <t xml:space="preserve">HEK 3xFLAG p21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2593,14 +7224,9 @@
           <t xml:space="preserve">HEK293T p14</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek gnt p21</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek gnt p21</t>
+          <t xml:space="preserve">HEK gNT p21</t>
         </is>
       </c>
     </row>
@@ -2672,19 +7298,9 @@
           <t xml:space="preserve">Huh7 p15</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">Huh7 3xFLAG p17</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 3xFLAG p17</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3 p18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2790,7 +7406,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnamed box  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">Unnamed box  ·  umut  ·  4/81 full</t>
         </is>
       </c>
     </row>
@@ -2848,6 +7464,26 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">klm ox</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jkl</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jkl</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jkl</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2881,6 +7517,670 @@
       <c r="A10" t="inlineStr">
         <is>
           <t xml:space="preserve">F</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box1  ·  baris  ·  26/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO 25.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO 25.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO 76.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO 76.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 P80 27.1.20 BARO 80.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box2  ·  baris  ·  54/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO 19+7</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO 19+7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO 19+7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO 19+7</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO 19+7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO 19+7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO 13.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO 13.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO 13.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO 34.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO 34.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO 55.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO 55.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO 55.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO 55.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO 55.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO 55.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO -</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO -</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO -</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO -</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR 20.07.20 BARO -</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR 20.07.20 BARO -</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO 46.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO 79.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO 76.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO 76.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 P84 08.07.20 BARO 84.0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO 7.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO 52.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO 52.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO 51.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO 51.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO 51.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO 51.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO 80.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO 77.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 P85 10.07.20 BARO 85.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO 29.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC) 36.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO -</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO -</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO 80.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO 77.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
         </is>
       </c>
     </row>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -8,7 +8,7 @@
     <sheet name="DUZENLE" sheetId="4" r:id="rId4"/>
     <sheet name="ONGOING" sheetId="5" r:id="rId5"/>
     <sheet name="UMUT CELLS -4-" sheetId="6" r:id="rId6"/>
-    <sheet name="Unnamed box" sheetId="7" r:id="rId7"/>
+    <sheet name="Common Box #1" sheetId="7" r:id="rId7"/>
     <sheet name="-80 Box1" sheetId="8" r:id="rId8"/>
     <sheet name="-80 Box2" sheetId="9" r:id="rId9"/>
     <sheet name="-80 Box3" sheetId="10" r:id="rId10"/>
@@ -288,13 +288,13 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6">
         <v>81</v>
       </c>
       <c r="I6">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -310,7 +310,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnamed box</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -325,13 +325,13 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>81</v>
       </c>
       <c r="I7">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
@@ -7094,7 +7094,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  36/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  37/81 full</t>
         </is>
       </c>
     </row>
@@ -7379,6 +7379,11 @@
       <c r="A12" t="inlineStr">
         <is>
           <t xml:space="preserve">H</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7411,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnamed box  ·  umut  ·  4/81 full</t>
+          <t xml:space="preserve">Common Box #1  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -7462,26 +7467,6 @@
       <c r="A5" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">klm ox</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jkl</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jkl</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jkl</t>
         </is>
       </c>
     </row>
